--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131150481</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>477517</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6595311</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131150481</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131150481</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131150481</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>132914412</v>
       </c>
       <c r="B4" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>132914412</v>
       </c>
       <c r="B4" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1401,6 +1401,258 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134226565</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477555</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6595400</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134226087</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477605</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6595369</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125740088</v>
       </c>
       <c r="B2" t="n">
-        <v>57816</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131150481</v>
+        <v>126556846</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,6 +825,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>i par</t>
@@ -835,16 +840,17 @@
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477517</v>
+        <v>477564</v>
       </c>
       <c r="R3" t="n">
-        <v>6595311</v>
+        <v>6595455</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,52 +919,62 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132914412</v>
+        <v>131150481</v>
       </c>
       <c r="B4" t="n">
-        <v>98005</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rockesholm, Vrm</t>
+          <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477397</v>
+        <v>477517</v>
       </c>
       <c r="R4" t="n">
-        <v>6595536</v>
+        <v>6595311</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,17 +998,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,12 +1028,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1022,7 +1043,7 @@
         <v>133011044</v>
       </c>
       <c r="B5" t="n">
-        <v>58119</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133039996</v>
+        <v>133015499</v>
       </c>
       <c r="B6" t="n">
-        <v>58119</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,20 +1209,20 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bofalla, Bofalla, Vrm</t>
+          <t>Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477688</v>
+        <v>477638</v>
       </c>
       <c r="R6" t="n">
-        <v>6595315</v>
+        <v>6595421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,27 +1249,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spel/sång i lämplig häckningsmiljö.</t>
+          <t>Spel/sång.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133040185</v>
+        <v>133039996</v>
       </c>
       <c r="B7" t="n">
-        <v>58119</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,10 +1347,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477544</v>
+        <v>477688</v>
       </c>
       <c r="R7" t="n">
-        <v>6595368</v>
+        <v>6595315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1392,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>05:51</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1403,7 +1424,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134226565</v>
+        <v>133040185</v>
       </c>
       <c r="B8" t="n">
         <v>58136</v>
@@ -1441,21 +1462,23 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bofalla, Bofalla, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477555</v>
+        <v>477544</v>
       </c>
       <c r="R8" t="n">
-        <v>6595400</v>
+        <v>6595368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,27 +1505,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>05:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Spel/sång.</t>
+          <t>Spel/sång i lämplig häckningsmiljö.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1653,6 +1676,345 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134226565</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>477555</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6595400</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spel/sång.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133012330</v>
+      </c>
+      <c r="B11" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bofalla, Bofalla, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>477484</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6595329</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132914412</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rockesholm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>477397</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6595536</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63185-2025 artfynd.xlsx
+++ b/artfynd/A 63185-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125740088</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126556846</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131150481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1165,6 +1185,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133011044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,6 +1318,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133015499</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1421,6 +1451,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133039996</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1549,6 +1584,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133040185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1675,6 +1715,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134226087</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1801,6 +1846,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134226565</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1908,6 +1958,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133012330</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2014,8 +2069,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132914412</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>